--- a/CDAX_Revenue_Financial_Performance_Dashboard.xlsx
+++ b/CDAX_Revenue_Financial_Performance_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pranit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54F68FC0-F9FE-4584-AB5B-1BBEF39DF460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F6E506-F890-4F77-8433-649731FE11B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="829" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Source_Courses!$A$1:$P$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Source_Purchases!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Source_Users!$A$1:$G$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$A$1:$I$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Financial_Alerts!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -1992,8 +1994,8 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5760000" cy="2880000"/>
     <xdr:graphicFrame macro="">
@@ -2695,7 +2697,7 @@
     <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageSetup scale="58" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2797,10 +2799,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2959,10 +2961,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3235,10 +3237,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="24" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3297,9 +3299,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageSetup scale="58" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3395,10 +3397,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3483,10 +3485,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3742,10 +3744,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="56" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3906,10 +3908,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4022,10 +4024,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4456,10 +4458,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>